--- a/artfynd/A 41869-2026 artfynd.xlsx
+++ b/artfynd/A 41869-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137233706</v>
+        <v>137243235</v>
       </c>
       <c r="B2" t="n">
-        <v>80616</v>
+        <v>80619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492806</v>
+        <v>492757</v>
       </c>
       <c r="R2" t="n">
-        <v>6824527</v>
+        <v>6824741</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,13 +776,1171 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137243235</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137243106</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kojvickoso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>492987</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6824775</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137243106</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137243230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kojvickoso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>492805</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6824752</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137243230</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137243276</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kojvickoso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>492720</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6824713</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137243276</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137243291</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kojvickoso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>492695</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6824701</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137243291</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137243314</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kojvickoso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>492689</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6824717</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137243314</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137243441</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kojvickoso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>492651</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6824593</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137243441</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137233706</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80618</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kojvickoso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>492806</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6824527</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137233706</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137243327</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80618</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Älgknopparna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>492545</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6824801</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Liten nyetablerad lunglav på aspens nordsida</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137243327</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137243310</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kojvickoso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>492689</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6824717</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137243310</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137243101</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58184</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kojvickoso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>492923</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6824716</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137243101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137243405</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58184</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Älgknopparna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>492445</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6824571</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137243405</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41869-2026 artfynd.xlsx
+++ b/artfynd/A 41869-2026 artfynd.xlsx
@@ -1647,11 +1647,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kojvickoso, Dlr</t>

--- a/artfynd/A 41869-2026 artfynd.xlsx
+++ b/artfynd/A 41869-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137243235</v>
       </c>
       <c r="B2" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137243106</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137243230</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137243276</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137243291</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137243314</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137243441</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137233706</v>
       </c>
       <c r="B9" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137243327</v>
       </c>
       <c r="B10" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137243310</v>
       </c>
       <c r="B11" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>137243101</v>
       </c>
       <c r="B12" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>137243405</v>
       </c>
       <c r="B13" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41869-2026 artfynd.xlsx
+++ b/artfynd/A 41869-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137243235</v>
       </c>
       <c r="B2" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137243106</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137243230</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137243276</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137243291</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137243314</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137243441</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137233706</v>
       </c>
       <c r="B9" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137243327</v>
       </c>
       <c r="B10" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137243310</v>
       </c>
       <c r="B11" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>137243101</v>
       </c>
       <c r="B12" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>137243405</v>
       </c>
       <c r="B13" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41869-2026 artfynd.xlsx
+++ b/artfynd/A 41869-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137243235</v>
       </c>
       <c r="B2" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137243106</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137243230</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137243276</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137243291</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137243314</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137243441</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137233706</v>
       </c>
       <c r="B9" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137243327</v>
       </c>
       <c r="B10" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137243310</v>
       </c>
       <c r="B11" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>137243101</v>
       </c>
       <c r="B12" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>137243405</v>
       </c>
       <c r="B13" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41869-2026 artfynd.xlsx
+++ b/artfynd/A 41869-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137243235</v>
       </c>
       <c r="B2" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137243106</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137243230</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137243276</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137243291</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137243314</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137243441</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137233706</v>
       </c>
       <c r="B9" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137243327</v>
       </c>
       <c r="B10" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41869-2026 artfynd.xlsx
+++ b/artfynd/A 41869-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137243235</v>
       </c>
       <c r="B2" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137243106</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137243230</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137243276</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137243291</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137243314</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137243441</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137233706</v>
       </c>
       <c r="B9" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137243327</v>
       </c>
       <c r="B10" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41869-2026 artfynd.xlsx
+++ b/artfynd/A 41869-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137243235</v>
       </c>
       <c r="B2" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137243106</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137243230</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137243276</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137243291</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137243314</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137243441</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137233706</v>
       </c>
       <c r="B9" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137243327</v>
       </c>
       <c r="B10" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 41869-2026 artfynd.xlsx
+++ b/artfynd/A 41869-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137243235</v>
       </c>
       <c r="B2" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137243106</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137243230</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137243276</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137243291</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137243314</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137243441</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137233706</v>
       </c>
       <c r="B9" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137243327</v>
       </c>
       <c r="B10" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>137243310</v>
       </c>
       <c r="B11" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>137243101</v>
       </c>
       <c r="B12" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>137243405</v>
       </c>
       <c r="B13" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
